--- a/deliverables/Onyx_TriNet_Questions.xlsx
+++ b/deliverables/Onyx_TriNet_Questions.xlsx
@@ -330,34 +330,34 @@
     <t xml:space="preserve">401(k)</t>
   </si>
   <si>
-    <t xml:space="preserve">Send the fund lineup with expense ratios, and name the target-date series.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">You disclose no lineup at all. The 0.14% average in your materials cannot be verified without it, and it is the figure that decides whether your 401(k) beats ADP's.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Empower as recordkeeper, TriNet as plan sponsor, and a 0.14% average with no holdings behind it.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.14% unverified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Also ask for the target-date series' own expense ratio, not just the plan average.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confirm Onyx pays nothing - no recordkeeping, no advisory, no base fee - and disclose any per-participant flat dollar fee on top of fund expenses.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">That is how we read your proposal, and it is currently your strongest advantage over Insperity, whose 401(k) bills the employer.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Our read of the TriNet proposal is $0 employer cost with all recurring cost on participants. Not explicitly confirmed.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$0 employer - our read</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Get it as a fee disclosure, not a sales statement.</t>
+    <t xml:space="preserve">What is the all-in expense ratio of your target-date series, and does the $63 participant fee come out on top of it?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One number settles retirement. We do not need the whole lineup - a five-person plan will sit almost entirely in the target-date funds. A 0.14% menu average is implausible for a lineup carrying American Funds and PIMCO.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADP has now published its full schedule in a DOL 404a-5 disclosure: target-date 0.48% all-in, NO participant account fee, recordkeeping funded by a 0.22% credit inside the funds. The $63 sets the crossover - if 0.14% is real TriNet wins above roughly $18,500 of balance; if their target-date is nearer 0.35% they are level with ADP at $50,000.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Settles retirement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Get the target-date figure in writing, not a plan average.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When does the $150 per hour for contribution allocation actually apply, and how many hours would a five-person plan with a match run in a year?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your own cost flyer lists no setup and no maintenance fee - but $1,000 to terminate, $150 per amendment, and $150 an hour for match, profit-sharing and true-up allocations. An owner-heavy S-corp plan needs that work every year, so 'no employer cost' is not accurate as written.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TriNet cost flyer, fees as of 01/2025. ADP discloses no employer charge of any kind - no setup, no recurring, no termination fee. These three items are now the whole difference between them on retirement cost.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$150/hr + $1,000 exit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ask for an annual dollar estimate, not just the hourly rate.</t>
   </si>
   <si>
     <t xml:space="preserve">As a multiple-employer plan where TriNet is the plan sponsor, does Onyx still qualify for the SECURE 2.0 startup and auto-enrollment credits?</t>
@@ -366,13 +366,13 @@
     <t xml:space="preserve">A real question, not a rhetorical one. The credits are worth meaningful money to a five-person firm and the answer depends on the plan structure, not on us.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nothing. Not addressed in any 401(k) material we hold.</t>
+    <t xml:space="preserve">Nothing, from either vendor. ADP is also a MEP with the PEO as plan sponsor, so the identical question goes to them and to our tax preparer.</t>
   </si>
   <si>
     <t xml:space="preserve">Tax credits</t>
   </si>
   <si>
-    <t xml:space="preserve">If the answer is no, price the same question at ADP - it may favor a standalone plan.</t>
+    <t xml:space="preserve">Worth up to $5,000/yr for three years plus $500/yr for auto-enrollment. If both MEPs disqualify us, price a standalone plan.</t>
   </si>
   <si>
     <t xml:space="preserve">Earliest realistic effective date, plus eligibility, entry dates, and whether Steven as 100% owner creates a top-heavy problem.</t>
@@ -1878,7 +1878,7 @@
         <v>100</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="D25" s="8" t="s">
         <v>101</v>
@@ -2340,8 +2340,8 @@
         <v>26</v>
       </c>
       <c r="D6" s="18" t="str">
-        <f aca="false">COUNTIF(Questions!$C$6:$C$37,"Ask first")&amp;" are ASK FIRST - the fee and the contribution floor"</f>
-        <v>5 are ASK FIRST - the fee and the contribution floor</v>
+        <f aca="false">COUNTIF(Questions!$C$6:$C$37,"Ask first")&amp;" are ASK FIRST - the service fee, the contribution floor and the target-date expense ratio"</f>
+        <v>6 are ASK FIRST - the service fee, the contribution floor and the target-date expense ratio</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
